--- a/stories/arbres/TREE-REL-015.xlsx
+++ b/stories/arbres/TREE-REL-015.xlsx
@@ -489,7 +489,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -831,6 +831,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -845,7 +857,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV87"/>
+  <dimension ref="A1:AW87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1139,6 +1151,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1163,7 +1180,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Nino est dans le train avec papa. Le train fait tchou. Un camarade est en face. Nino a un petit livre. Papa dit : tu peux inviter. Tu veux jouer avec nous. Un non est possible.</t>
+          <t>Nino est dans le train avec papa. Le train fait tchou. Un camarade est en face. Nino a un petit livre. Tu peux inviter. Tu veux jouer avec nous. Un non est possible.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1301,6 +1318,13 @@
         <v>12</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Nino est dans le train avec papa. Le train fait tchou. Un camarade est en face. Nino a un petit livre.
+papa|Tu peux inviter. Tu veux jouer avec nous.
+narrateur|Un non est possible.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1487,6 +1511,11 @@
         <v>12</v>
       </c>
       <c r="AV3" s="2" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le siège, le couloir, ou la tablette.</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1645,6 +1674,11 @@
         <v>12</v>
       </c>
       <c r="AV4" s="2" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Nino va vers le siège. Le siège est souple. papa est tout près. Nino invite. Nino invite. Il accepte un non. papa sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1821,6 +1855,11 @@
       <c r="AV5" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Nino veut un camarade. Que dit-il ?</t>
         </is>
       </c>
     </row>
@@ -1985,6 +2024,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|Oui. Nino a retenu. Nino invite. Il accepte un non. On continue avec papa.</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -2173,6 +2217,11 @@
       <c r="AV7" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre Léa, Tom, ou Sara.</t>
         </is>
       </c>
     </row>
@@ -2333,6 +2382,11 @@
         <v>12</v>
       </c>
       <c r="AV8" s="2" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>narrateur|Nino a choisi Léa. Un paysage file. papa montre lentement. Nino demande : tu veux jouer. Nino invite. Il accepte un non. maman n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -2519,6 +2573,11 @@
         <v>12</v>
       </c>
       <c r="AV9" s="2" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre un oui, un non, ou plus tard.</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -2677,6 +2736,11 @@
         <v>12</v>
       </c>
       <c r="AV10" s="2" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>narrateur|Nino rejoint un oui. Les roues chantent. Nino invite. Nino invite. Il accepte un non. papa dit merci. le siège, puis Léa.</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -2839,6 +2903,11 @@
         <v>12</v>
       </c>
       <c r="AV11" s="2" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -2997,6 +3066,11 @@
         <v>12</v>
       </c>
       <c r="AV12" s="2" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>narrateur|Nino rejoint un non. La lumière passe. Nino demande : tu veux jouer. Nino invite. Il accepte un non. papa dit merci. le siège, puis Léa.</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -3159,6 +3233,11 @@
         <v>12</v>
       </c>
       <c r="AV13" s="2" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -3317,6 +3396,11 @@
         <v>12</v>
       </c>
       <c r="AV14" s="2" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>narrateur|Nino rejoint plus tard. Un goûter est dans le sac. Nino accepte le non. Nino invite. Il accepte un non. papa dit merci. le siège, puis Léa.</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -3479,6 +3563,11 @@
         <v>12</v>
       </c>
       <c r="AV15" s="2" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -3637,6 +3726,11 @@
         <v>12</v>
       </c>
       <c r="AV16" s="2" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>narrateur|Nino a choisi Tom. Papa est près. papa montre lentement. Nino accepte le non. Nino invite. Il accepte un non. maman n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -3823,6 +3917,11 @@
         <v>12</v>
       </c>
       <c r="AV17" s="2" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre un oui, un non, ou plus tard.</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -3981,6 +4080,11 @@
         <v>12</v>
       </c>
       <c r="AV18" s="2" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>narrateur|Nino rejoint un oui. La lumière passe. Nino demande : tu veux jouer. Nino invite. Il accepte un non. papa dit merci. le siège, puis Tom.</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -4143,6 +4247,11 @@
         <v>12</v>
       </c>
       <c r="AV19" s="2" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -4301,6 +4410,11 @@
         <v>12</v>
       </c>
       <c r="AV20" s="2" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>narrateur|Nino rejoint un non. Un goûter est dans le sac. Nino accepte le non. Nino invite. Il accepte un non. papa dit merci. le siège, puis Tom.</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -4463,6 +4577,11 @@
         <v>12</v>
       </c>
       <c r="AV21" s="2" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -4621,6 +4740,11 @@
         <v>12</v>
       </c>
       <c r="AV22" s="2" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>narrateur|Nino rejoint plus tard. Le couloir est calme. Nino reste avec papa. Nino invite. Il accepte un non. papa dit merci. le siège, puis Tom.</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -4783,6 +4907,11 @@
         <v>12</v>
       </c>
       <c r="AV23" s="2" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -4941,6 +5070,11 @@
         <v>12</v>
       </c>
       <c r="AV24" s="2" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>narrateur|Nino a choisi Sara. Un livre sent le papier. papa montre lentement. Nino reste avec papa. Nino invite. Il accepte un non. maman n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -5127,6 +5261,11 @@
         <v>12</v>
       </c>
       <c r="AV25" s="2" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre un oui, un non, ou plus tard.</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -5285,6 +5424,11 @@
         <v>12</v>
       </c>
       <c r="AV26" s="2" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>narrateur|Nino rejoint un oui. Un goûter est dans le sac. Nino accepte le non. Nino invite. Il accepte un non. papa dit merci. le siège, puis Sara.</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -5447,6 +5591,11 @@
         <v>12</v>
       </c>
       <c r="AV27" s="2" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -5605,6 +5754,11 @@
         <v>12</v>
       </c>
       <c r="AV28" s="2" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>narrateur|Nino rejoint un non. Le couloir est calme. Nino reste avec papa. Nino invite. Il accepte un non. papa dit merci. le siège, puis Sara.</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -5767,6 +5921,11 @@
         <v>12</v>
       </c>
       <c r="AV29" s="2" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -5925,6 +6084,11 @@
         <v>12</v>
       </c>
       <c r="AV30" s="2" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>narrateur|Nino rejoint plus tard. Un sourire arrive. Nino propose le livre. Nino invite. Il accepte un non. papa dit merci. le siège, puis Sara.</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -6087,6 +6251,11 @@
         <v>12</v>
       </c>
       <c r="AV31" s="2" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -6245,6 +6414,11 @@
         <v>12</v>
       </c>
       <c r="AV32" s="2" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>narrateur|Nino va vers le couloir. Le train vibre. papa est tout près. Nino demande : tu veux jouer. Nino invite. Il accepte un non. papa sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -6423,6 +6597,11 @@
           <t>question d'écoute, ne change pas le cours</t>
         </is>
       </c>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>narrateur|Nino veut un camarade. Que dit-il ?</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
@@ -6447,7 +6626,7 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>Nino respire. Nino invite. Il accepte un non. papa dit : je suis là.</t>
+          <t>Nino respire. Nino invite. Il accepte un non. Je suis là.</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
@@ -6585,6 +6764,12 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>narrateur|Nino respire. Nino invite. Il accepte un non.
+papa|Je suis là.</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -6773,6 +6958,11 @@
       <c r="AV35" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre Léa, Tom, ou Sara.</t>
         </is>
       </c>
     </row>
@@ -6933,6 +7123,11 @@
         <v>12</v>
       </c>
       <c r="AV36" s="2" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>narrateur|Nino a choisi Léa. Les roues chantent. papa montre lentement. Nino accepte le non. Nino invite. Il accepte un non. maman n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -7119,6 +7314,11 @@
         <v>12</v>
       </c>
       <c r="AV37" s="2" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre un oui, un non, ou plus tard.</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -7277,6 +7477,11 @@
         <v>12</v>
       </c>
       <c r="AV38" s="2" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>narrateur|Nino rejoint un oui. La lumière passe. Nino invite. Nino invite. Il accepte un non. papa dit merci. le couloir, puis Léa.</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -7439,6 +7644,11 @@
         <v>12</v>
       </c>
       <c r="AV39" s="2" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -7597,6 +7807,11 @@
         <v>12</v>
       </c>
       <c r="AV40" s="2" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>narrateur|Nino rejoint un non. Un goûter est dans le sac. Nino demande : tu veux jouer. Nino invite. Il accepte un non. papa dit merci. le couloir, puis Léa.</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -7759,6 +7974,11 @@
         <v>12</v>
       </c>
       <c r="AV41" s="2" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -7917,6 +8137,11 @@
         <v>12</v>
       </c>
       <c r="AV42" s="2" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>narrateur|Nino rejoint plus tard. Le couloir est calme. Nino accepte le non. Nino invite. Il accepte un non. papa dit merci. le couloir, puis Léa.</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -8079,6 +8304,11 @@
         <v>12</v>
       </c>
       <c r="AV43" s="2" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -8237,6 +8467,11 @@
         <v>12</v>
       </c>
       <c r="AV44" s="2" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>narrateur|Nino a choisi Tom. La lumière passe. papa montre lentement. Nino reste avec papa. Nino invite. Il accepte un non. maman n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -8423,6 +8658,11 @@
         <v>12</v>
       </c>
       <c r="AV45" s="2" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre un oui, un non, ou plus tard.</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
@@ -8581,6 +8821,11 @@
         <v>12</v>
       </c>
       <c r="AV46" s="2" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>narrateur|Nino rejoint un oui. Un goûter est dans le sac. Nino demande : tu veux jouer. Nino invite. Il accepte un non. papa dit merci. le couloir, puis Tom.</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -8743,6 +8988,11 @@
         <v>12</v>
       </c>
       <c r="AV47" s="2" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -8901,6 +9151,11 @@
         <v>12</v>
       </c>
       <c r="AV48" s="2" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>narrateur|Nino rejoint un non. Le couloir est calme. Nino accepte le non. Nino invite. Il accepte un non. papa dit merci. le couloir, puis Tom.</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -9063,6 +9318,11 @@
         <v>12</v>
       </c>
       <c r="AV49" s="2" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -9221,6 +9481,11 @@
         <v>12</v>
       </c>
       <c r="AV50" s="2" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>narrateur|Nino rejoint plus tard. Un sourire arrive. Nino reste avec papa. Nino invite. Il accepte un non. papa dit merci. le couloir, puis Tom.</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -9383,6 +9648,11 @@
         <v>12</v>
       </c>
       <c r="AV51" s="2" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -9541,6 +9811,11 @@
         <v>12</v>
       </c>
       <c r="AV52" s="2" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>narrateur|Nino a choisi Sara. Un goûter est dans le sac. papa montre lentement. Nino propose le livre. Nino invite. Il accepte un non. maman n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -9727,6 +10002,11 @@
         <v>12</v>
       </c>
       <c r="AV53" s="2" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre un oui, un non, ou plus tard.</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
@@ -9885,6 +10165,11 @@
         <v>12</v>
       </c>
       <c r="AV54" s="2" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>narrateur|Nino rejoint un oui. Le couloir est calme. Nino accepte le non. Nino invite. Il accepte un non. papa dit merci. le couloir, puis Sara.</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -10047,6 +10332,11 @@
         <v>12</v>
       </c>
       <c r="AV55" s="2" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -10205,6 +10495,11 @@
         <v>12</v>
       </c>
       <c r="AV56" s="2" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>narrateur|Nino rejoint un non. Un sourire arrive. Nino reste avec papa. Nino invite. Il accepte un non. papa dit merci. le couloir, puis Sara.</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -10367,6 +10662,11 @@
         <v>12</v>
       </c>
       <c r="AV57" s="2" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -10525,6 +10825,11 @@
         <v>12</v>
       </c>
       <c r="AV58" s="2" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>narrateur|Nino rejoint plus tard. Le ciel est gris. Nino propose le livre. Nino invite. Il accepte un non. papa dit merci. le couloir, puis Sara.</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -10687,6 +10992,11 @@
         <v>12</v>
       </c>
       <c r="AV59" s="2" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -10845,6 +11155,11 @@
         <v>12</v>
       </c>
       <c r="AV60" s="2" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>narrateur|Nino va vers la tablette. La tablette est lisse. papa est tout près. Nino accepte le non. Nino invite. Il accepte un non. papa sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -11021,6 +11336,11 @@
       <c r="AV61" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>narrateur|Nino veut un camarade. Que dit-il ?</t>
         </is>
       </c>
     </row>
@@ -11189,6 +11509,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>narrateur|C'est juste. Nino invite. Il accepte un non. Nino donne la main à papa.</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -11377,6 +11702,11 @@
       <c r="AV63" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre Léa, Tom, ou Sara.</t>
         </is>
       </c>
     </row>
@@ -11537,6 +11867,11 @@
         <v>12</v>
       </c>
       <c r="AV64" s="2" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>narrateur|Nino a choisi Léa. Le couloir est calme. papa montre lentement. Nino reste avec papa. Nino invite. Il accepte un non. maman n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -11723,6 +12058,11 @@
         <v>12</v>
       </c>
       <c r="AV65" s="2" t="inlineStr"/>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre un oui, un non, ou plus tard.</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
@@ -11881,6 +12221,11 @@
         <v>12</v>
       </c>
       <c r="AV66" s="2" t="inlineStr"/>
+      <c r="AW66" t="inlineStr">
+        <is>
+          <t>narrateur|Nino rejoint un oui. Un goûter est dans le sac. Nino invite. Nino invite. Il accepte un non. papa dit merci. la tablette, puis Léa.</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -12043,6 +12388,11 @@
         <v>12</v>
       </c>
       <c r="AV67" s="2" t="inlineStr"/>
+      <c r="AW67" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -12201,6 +12551,11 @@
         <v>12</v>
       </c>
       <c r="AV68" s="2" t="inlineStr"/>
+      <c r="AW68" t="inlineStr">
+        <is>
+          <t>narrateur|Nino rejoint un non. Le couloir est calme. Nino demande : tu veux jouer. Nino invite. Il accepte un non. papa dit merci. la tablette, puis Léa.</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -12363,6 +12718,11 @@
         <v>12</v>
       </c>
       <c r="AV69" s="2" t="inlineStr"/>
+      <c r="AW69" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -12521,6 +12881,11 @@
         <v>12</v>
       </c>
       <c r="AV70" s="2" t="inlineStr"/>
+      <c r="AW70" t="inlineStr">
+        <is>
+          <t>narrateur|Nino rejoint plus tard. Un sourire arrive. Nino accepte le non. Nino invite. Il accepte un non. papa dit merci. la tablette, puis Léa.</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -12683,6 +13048,11 @@
         <v>12</v>
       </c>
       <c r="AV71" s="2" t="inlineStr"/>
+      <c r="AW71" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
@@ -12841,6 +13211,11 @@
         <v>12</v>
       </c>
       <c r="AV72" s="2" t="inlineStr"/>
+      <c r="AW72" t="inlineStr">
+        <is>
+          <t>narrateur|Nino a choisi Tom. Un sourire arrive. papa montre lentement. Nino propose le livre. Nino invite. Il accepte un non. maman n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -13027,6 +13402,11 @@
         <v>12</v>
       </c>
       <c r="AV73" s="2" t="inlineStr"/>
+      <c r="AW73" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre un oui, un non, ou plus tard.</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
@@ -13185,6 +13565,11 @@
         <v>12</v>
       </c>
       <c r="AV74" s="2" t="inlineStr"/>
+      <c r="AW74" t="inlineStr">
+        <is>
+          <t>narrateur|Nino rejoint un oui. Le couloir est calme. Nino demande : tu veux jouer. Nino invite. Il accepte un non. papa dit merci. la tablette, puis Tom.</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
@@ -13347,6 +13732,11 @@
         <v>12</v>
       </c>
       <c r="AV75" s="2" t="inlineStr"/>
+      <c r="AW75" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
@@ -13505,6 +13895,11 @@
         <v>12</v>
       </c>
       <c r="AV76" s="2" t="inlineStr"/>
+      <c r="AW76" t="inlineStr">
+        <is>
+          <t>narrateur|Nino rejoint un non. Un sourire arrive. Nino accepte le non. Nino invite. Il accepte un non. papa dit merci. la tablette, puis Tom.</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -13667,6 +14062,11 @@
         <v>12</v>
       </c>
       <c r="AV77" s="2" t="inlineStr"/>
+      <c r="AW77" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
@@ -13825,6 +14225,11 @@
         <v>12</v>
       </c>
       <c r="AV78" s="2" t="inlineStr"/>
+      <c r="AW78" t="inlineStr">
+        <is>
+          <t>narrateur|Nino rejoint plus tard. Le ciel est gris. Nino reste avec papa. Nino invite. Il accepte un non. papa dit merci. la tablette, puis Tom.</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
@@ -13987,6 +14392,11 @@
         <v>12</v>
       </c>
       <c r="AV79" s="2" t="inlineStr"/>
+      <c r="AW79" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
@@ -14145,6 +14555,11 @@
         <v>12</v>
       </c>
       <c r="AV80" s="2" t="inlineStr"/>
+      <c r="AW80" t="inlineStr">
+        <is>
+          <t>narrateur|Nino a choisi Sara. Le ciel est gris. papa montre lentement. Nino invite. Nino invite. Il accepte un non. maman n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
@@ -14331,6 +14746,11 @@
         <v>12</v>
       </c>
       <c r="AV81" s="2" t="inlineStr"/>
+      <c r="AW81" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre un oui, un non, ou plus tard.</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
@@ -14489,6 +14909,11 @@
         <v>12</v>
       </c>
       <c r="AV82" s="2" t="inlineStr"/>
+      <c r="AW82" t="inlineStr">
+        <is>
+          <t>narrateur|Nino rejoint un oui. Un sourire arrive. Nino accepte le non. Nino invite. Il accepte un non. papa dit merci. la tablette, puis Sara.</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
@@ -14651,6 +15076,11 @@
         <v>12</v>
       </c>
       <c r="AV83" s="2" t="inlineStr"/>
+      <c r="AW83" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
@@ -14809,6 +15239,11 @@
         <v>12</v>
       </c>
       <c r="AV84" s="2" t="inlineStr"/>
+      <c r="AW84" t="inlineStr">
+        <is>
+          <t>narrateur|Nino rejoint un non. Le ciel est gris. Nino reste avec papa. Nino invite. Il accepte un non. papa dit merci. la tablette, puis Sara.</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
@@ -14971,6 +15406,11 @@
         <v>12</v>
       </c>
       <c r="AV85" s="2" t="inlineStr"/>
+      <c r="AW85" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
@@ -15129,6 +15569,11 @@
         <v>12</v>
       </c>
       <c r="AV86" s="2" t="inlineStr"/>
+      <c r="AW86" t="inlineStr">
+        <is>
+          <t>narrateur|Nino rejoint plus tard. Le siège est souple. Nino propose le livre. Nino invite. Il accepte un non. papa dit merci. la tablette, puis Sara.</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
@@ -15291,6 +15736,11 @@
         <v>12</v>
       </c>
       <c r="AV87" s="2" t="inlineStr"/>
+      <c r="AW87" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV87"/>
@@ -15309,7 +15759,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A4"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -15340,6 +15790,13 @@
       <c r="A4" t="inlineStr">
         <is>
           <t>ch2C: prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/TREE-REL-015.xlsx
+++ b/stories/arbres/TREE-REL-015.xlsx
@@ -857,7 +857,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW87"/>
+  <dimension ref="A1:AX87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1156,6 +1156,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1325,6 +1330,7 @@
 narrateur|Un non est possible.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1516,6 +1522,7 @@
           <t>narrateur|On peut prendre le siège, le couloir, ou la tablette.</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1679,6 +1686,7 @@
           <t>narrateur|Nino va vers le siège. Le siège est souple. papa est tout près. Nino invite. Nino invite. Il accepte un non. papa sourit.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1862,6 +1870,7 @@
           <t>narrateur|Nino veut un camarade. Que dit-il ?</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -2029,6 +2038,7 @@
           <t>narrateur|Oui. Nino a retenu. Nino invite. Il accepte un non. On continue avec papa.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -2224,6 +2234,7 @@
           <t>narrateur|On peut prendre Léa, Tom, ou Sara.</t>
         </is>
       </c>
+      <c r="AX7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -2387,6 +2398,7 @@
           <t>narrateur|Nino a choisi Léa. Un paysage file. papa montre lentement. Nino demande : tu veux jouer. Nino invite. Il accepte un non. maman n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -2578,6 +2590,7 @@
           <t>narrateur|On peut prendre un oui, un non, ou plus tard.</t>
         </is>
       </c>
+      <c r="AX9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -2741,6 +2754,7 @@
           <t>narrateur|Nino rejoint un oui. Les roues chantent. Nino invite. Nino invite. Il accepte un non. papa dit merci. le siège, puis Léa.</t>
         </is>
       </c>
+      <c r="AX10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -2908,6 +2922,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -3071,6 +3086,7 @@
           <t>narrateur|Nino rejoint un non. La lumière passe. Nino demande : tu veux jouer. Nino invite. Il accepte un non. papa dit merci. le siège, puis Léa.</t>
         </is>
       </c>
+      <c r="AX12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -3238,6 +3254,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -3401,6 +3418,7 @@
           <t>narrateur|Nino rejoint plus tard. Un goûter est dans le sac. Nino accepte le non. Nino invite. Il accepte un non. papa dit merci. le siège, puis Léa.</t>
         </is>
       </c>
+      <c r="AX14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -3568,6 +3586,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -3731,6 +3750,7 @@
           <t>narrateur|Nino a choisi Tom. Papa est près. papa montre lentement. Nino accepte le non. Nino invite. Il accepte un non. maman n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -3922,6 +3942,7 @@
           <t>narrateur|On peut prendre un oui, un non, ou plus tard.</t>
         </is>
       </c>
+      <c r="AX17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -4085,6 +4106,7 @@
           <t>narrateur|Nino rejoint un oui. La lumière passe. Nino demande : tu veux jouer. Nino invite. Il accepte un non. papa dit merci. le siège, puis Tom.</t>
         </is>
       </c>
+      <c r="AX18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -4252,6 +4274,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -4415,6 +4438,7 @@
           <t>narrateur|Nino rejoint un non. Un goûter est dans le sac. Nino accepte le non. Nino invite. Il accepte un non. papa dit merci. le siège, puis Tom.</t>
         </is>
       </c>
+      <c r="AX20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -4582,6 +4606,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -4745,6 +4770,7 @@
           <t>narrateur|Nino rejoint plus tard. Le couloir est calme. Nino reste avec papa. Nino invite. Il accepte un non. papa dit merci. le siège, puis Tom.</t>
         </is>
       </c>
+      <c r="AX22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -4912,6 +4938,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -5075,6 +5102,7 @@
           <t>narrateur|Nino a choisi Sara. Un livre sent le papier. papa montre lentement. Nino reste avec papa. Nino invite. Il accepte un non. maman n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -5266,6 +5294,7 @@
           <t>narrateur|On peut prendre un oui, un non, ou plus tard.</t>
         </is>
       </c>
+      <c r="AX25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -5429,6 +5458,7 @@
           <t>narrateur|Nino rejoint un oui. Un goûter est dans le sac. Nino accepte le non. Nino invite. Il accepte un non. papa dit merci. le siège, puis Sara.</t>
         </is>
       </c>
+      <c r="AX26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -5596,6 +5626,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -5759,6 +5790,7 @@
           <t>narrateur|Nino rejoint un non. Le couloir est calme. Nino reste avec papa. Nino invite. Il accepte un non. papa dit merci. le siège, puis Sara.</t>
         </is>
       </c>
+      <c r="AX28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -5926,6 +5958,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -6089,6 +6122,7 @@
           <t>narrateur|Nino rejoint plus tard. Un sourire arrive. Nino propose le livre. Nino invite. Il accepte un non. papa dit merci. le siège, puis Sara.</t>
         </is>
       </c>
+      <c r="AX30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -6256,6 +6290,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -6419,6 +6454,7 @@
           <t>narrateur|Nino va vers le couloir. Le train vibre. papa est tout près. Nino demande : tu veux jouer. Nino invite. Il accepte un non. papa sourit.</t>
         </is>
       </c>
+      <c r="AX32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -6602,6 +6638,7 @@
           <t>narrateur|Nino veut un camarade. Que dit-il ?</t>
         </is>
       </c>
+      <c r="AX33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
@@ -6770,6 +6807,7 @@
 papa|Je suis là.</t>
         </is>
       </c>
+      <c r="AX34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -6965,6 +7003,7 @@
           <t>narrateur|On peut prendre Léa, Tom, ou Sara.</t>
         </is>
       </c>
+      <c r="AX35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -7128,6 +7167,7 @@
           <t>narrateur|Nino a choisi Léa. Les roues chantent. papa montre lentement. Nino accepte le non. Nino invite. Il accepte un non. maman n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -7319,6 +7359,7 @@
           <t>narrateur|On peut prendre un oui, un non, ou plus tard.</t>
         </is>
       </c>
+      <c r="AX37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -7482,6 +7523,7 @@
           <t>narrateur|Nino rejoint un oui. La lumière passe. Nino invite. Nino invite. Il accepte un non. papa dit merci. le couloir, puis Léa.</t>
         </is>
       </c>
+      <c r="AX38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -7649,6 +7691,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -7812,6 +7855,7 @@
           <t>narrateur|Nino rejoint un non. Un goûter est dans le sac. Nino demande : tu veux jouer. Nino invite. Il accepte un non. papa dit merci. le couloir, puis Léa.</t>
         </is>
       </c>
+      <c r="AX40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -7979,6 +8023,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -8142,6 +8187,7 @@
           <t>narrateur|Nino rejoint plus tard. Le couloir est calme. Nino accepte le non. Nino invite. Il accepte un non. papa dit merci. le couloir, puis Léa.</t>
         </is>
       </c>
+      <c r="AX42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -8309,6 +8355,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -8472,6 +8519,7 @@
           <t>narrateur|Nino a choisi Tom. La lumière passe. papa montre lentement. Nino reste avec papa. Nino invite. Il accepte un non. maman n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -8663,6 +8711,7 @@
           <t>narrateur|On peut prendre un oui, un non, ou plus tard.</t>
         </is>
       </c>
+      <c r="AX45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
@@ -8826,6 +8875,7 @@
           <t>narrateur|Nino rejoint un oui. Un goûter est dans le sac. Nino demande : tu veux jouer. Nino invite. Il accepte un non. papa dit merci. le couloir, puis Tom.</t>
         </is>
       </c>
+      <c r="AX46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -8993,6 +9043,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -9156,6 +9207,7 @@
           <t>narrateur|Nino rejoint un non. Le couloir est calme. Nino accepte le non. Nino invite. Il accepte un non. papa dit merci. le couloir, puis Tom.</t>
         </is>
       </c>
+      <c r="AX48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -9323,6 +9375,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -9486,6 +9539,7 @@
           <t>narrateur|Nino rejoint plus tard. Un sourire arrive. Nino reste avec papa. Nino invite. Il accepte un non. papa dit merci. le couloir, puis Tom.</t>
         </is>
       </c>
+      <c r="AX50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -9653,6 +9707,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -9816,6 +9871,7 @@
           <t>narrateur|Nino a choisi Sara. Un goûter est dans le sac. papa montre lentement. Nino propose le livre. Nino invite. Il accepte un non. maman n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -10007,6 +10063,7 @@
           <t>narrateur|On peut prendre un oui, un non, ou plus tard.</t>
         </is>
       </c>
+      <c r="AX53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
@@ -10170,6 +10227,7 @@
           <t>narrateur|Nino rejoint un oui. Le couloir est calme. Nino accepte le non. Nino invite. Il accepte un non. papa dit merci. le couloir, puis Sara.</t>
         </is>
       </c>
+      <c r="AX54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -10337,6 +10395,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -10500,6 +10559,7 @@
           <t>narrateur|Nino rejoint un non. Un sourire arrive. Nino reste avec papa. Nino invite. Il accepte un non. papa dit merci. le couloir, puis Sara.</t>
         </is>
       </c>
+      <c r="AX56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -10667,6 +10727,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -10830,6 +10891,7 @@
           <t>narrateur|Nino rejoint plus tard. Le ciel est gris. Nino propose le livre. Nino invite. Il accepte un non. papa dit merci. le couloir, puis Sara.</t>
         </is>
       </c>
+      <c r="AX58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -10997,6 +11059,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -11160,6 +11223,7 @@
           <t>narrateur|Nino va vers la tablette. La tablette est lisse. papa est tout près. Nino accepte le non. Nino invite. Il accepte un non. papa sourit.</t>
         </is>
       </c>
+      <c r="AX60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -11343,6 +11407,7 @@
           <t>narrateur|Nino veut un camarade. Que dit-il ?</t>
         </is>
       </c>
+      <c r="AX61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
@@ -11514,6 +11579,7 @@
           <t>narrateur|C'est juste. Nino invite. Il accepte un non. Nino donne la main à papa.</t>
         </is>
       </c>
+      <c r="AX62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -11709,6 +11775,7 @@
           <t>narrateur|On peut prendre Léa, Tom, ou Sara.</t>
         </is>
       </c>
+      <c r="AX63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
@@ -11872,6 +11939,7 @@
           <t>narrateur|Nino a choisi Léa. Le couloir est calme. papa montre lentement. Nino reste avec papa. Nino invite. Il accepte un non. maman n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -12063,6 +12131,7 @@
           <t>narrateur|On peut prendre un oui, un non, ou plus tard.</t>
         </is>
       </c>
+      <c r="AX65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
@@ -12226,6 +12295,7 @@
           <t>narrateur|Nino rejoint un oui. Un goûter est dans le sac. Nino invite. Nino invite. Il accepte un non. papa dit merci. la tablette, puis Léa.</t>
         </is>
       </c>
+      <c r="AX66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -12393,6 +12463,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -12556,6 +12627,7 @@
           <t>narrateur|Nino rejoint un non. Le couloir est calme. Nino demande : tu veux jouer. Nino invite. Il accepte un non. papa dit merci. la tablette, puis Léa.</t>
         </is>
       </c>
+      <c r="AX68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -12723,6 +12795,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -12886,6 +12959,7 @@
           <t>narrateur|Nino rejoint plus tard. Un sourire arrive. Nino accepte le non. Nino invite. Il accepte un non. papa dit merci. la tablette, puis Léa.</t>
         </is>
       </c>
+      <c r="AX70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -13053,6 +13127,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
@@ -13216,6 +13291,7 @@
           <t>narrateur|Nino a choisi Tom. Un sourire arrive. papa montre lentement. Nino propose le livre. Nino invite. Il accepte un non. maman n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -13407,6 +13483,7 @@
           <t>narrateur|On peut prendre un oui, un non, ou plus tard.</t>
         </is>
       </c>
+      <c r="AX73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
@@ -13570,6 +13647,7 @@
           <t>narrateur|Nino rejoint un oui. Le couloir est calme. Nino demande : tu veux jouer. Nino invite. Il accepte un non. papa dit merci. la tablette, puis Tom.</t>
         </is>
       </c>
+      <c r="AX74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
@@ -13737,6 +13815,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
@@ -13900,6 +13979,7 @@
           <t>narrateur|Nino rejoint un non. Un sourire arrive. Nino accepte le non. Nino invite. Il accepte un non. papa dit merci. la tablette, puis Tom.</t>
         </is>
       </c>
+      <c r="AX76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -14067,6 +14147,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
@@ -14230,6 +14311,7 @@
           <t>narrateur|Nino rejoint plus tard. Le ciel est gris. Nino reste avec papa. Nino invite. Il accepte un non. papa dit merci. la tablette, puis Tom.</t>
         </is>
       </c>
+      <c r="AX78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
@@ -14397,6 +14479,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
@@ -14560,6 +14643,7 @@
           <t>narrateur|Nino a choisi Sara. Le ciel est gris. papa montre lentement. Nino invite. Nino invite. Il accepte un non. maman n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
@@ -14751,6 +14835,7 @@
           <t>narrateur|On peut prendre un oui, un non, ou plus tard.</t>
         </is>
       </c>
+      <c r="AX81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
@@ -14914,6 +14999,7 @@
           <t>narrateur|Nino rejoint un oui. Un sourire arrive. Nino accepte le non. Nino invite. Il accepte un non. papa dit merci. la tablette, puis Sara.</t>
         </is>
       </c>
+      <c r="AX82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
@@ -15081,6 +15167,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
@@ -15244,6 +15331,7 @@
           <t>narrateur|Nino rejoint un non. Le ciel est gris. Nino reste avec papa. Nino invite. Il accepte un non. papa dit merci. la tablette, puis Sara.</t>
         </is>
       </c>
+      <c r="AX84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
@@ -15411,6 +15499,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
@@ -15574,6 +15663,7 @@
           <t>narrateur|Nino rejoint plus tard. Le siège est souple. Nino propose le livre. Nino invite. Il accepte un non. papa dit merci. la tablette, puis Sara.</t>
         </is>
       </c>
+      <c r="AX86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
@@ -15741,6 +15831,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX87" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV87"/>
@@ -15759,7 +15850,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -15797,6 +15888,20 @@
       <c r="A5" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -15811,7 +15916,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -15998,6 +16103,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
